--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:35:29+00:00</t>
+    <t>2026-08-28T09:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:07:16+00:00</t>
+    <t>2026-08-28T12:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:09:44+00:00</t>
+    <t>2026-08-28T12:57:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:57:14+00:00</t>
+    <t>2026-08-28T14:34:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:34:56+00:00</t>
+    <t>2026-08-31T19:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-muv-arterieller-blutdruck.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$252</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7997" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8223" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.3</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:08:04+00:00</t>
+    <t>2026-08-31T19:21:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2181,6 +2181,27 @@
   </si>
   <si>
     <t>Observation.component:meanBP.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].value</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].comparator</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].unit</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].system</t>
+  </si>
+  <si>
+    <t>Observation.component:meanBP.value[x].code</t>
   </si>
   <si>
     <t>Observation.component:meanBP.value[x]:valueQuantity</t>
@@ -2528,7 +2549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ245"/>
+  <dimension ref="A1:AJ252"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.48046875" customWidth="true" bestFit="true"/>
@@ -26663,11 +26684,9 @@
         <v>678</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C235" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
         <v>75</v>
       </c>
@@ -26685,23 +26704,19 @@
         <v>75</v>
       </c>
       <c r="J235" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>319</v>
+        <v>190</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>485</v>
+        <v>191</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>75</v>
       </c>
@@ -26710,7 +26725,7 @@
         <v>75</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>571</v>
+        <v>75</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>75</v>
@@ -26749,7 +26764,7 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>483</v>
+        <v>193</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>73</v>
@@ -26758,10 +26773,10 @@
         <v>82</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="236" hidden="true">
@@ -26769,18 +26784,18 @@
         <v>679</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>75</v>
@@ -26792,15 +26807,17 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N236" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>75</v>
@@ -26837,73 +26854,75 @@
         <v>75</v>
       </c>
       <c r="AB236" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="AC236" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AD236" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE236" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>75</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="237" hidden="true">
+    <row r="237">
       <c r="A237" t="s" s="2">
         <v>680</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J237" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>127</v>
+        <v>326</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>195</v>
+        <v>328</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O237" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P237" t="s" s="2">
         <v>75</v>
       </c>
@@ -26939,31 +26958,31 @@
         <v>75</v>
       </c>
       <c r="AB237" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="AC237" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AD237" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE237" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>196</v>
+        <v>331</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>135</v>
+        <v>90</v>
       </c>
     </row>
     <row r="238" hidden="true">
@@ -26971,7 +26990,7 @@
         <v>681</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26979,7 +26998,7 @@
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G238" t="s" s="2">
         <v>82</v>
@@ -26988,30 +27007,30 @@
         <v>75</v>
       </c>
       <c r="I238" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J238" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>326</v>
+        <v>103</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q238" s="2"/>
+      <c r="Q238" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="R238" t="s" s="2">
         <v>75</v>
       </c>
@@ -27031,13 +27050,13 @@
         <v>75</v>
       </c>
       <c r="X238" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y238" t="s" s="2">
-        <v>75</v>
+        <v>338</v>
       </c>
       <c r="Z238" t="s" s="2">
-        <v>75</v>
+        <v>339</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>75</v>
@@ -27055,7 +27074,7 @@
         <v>75</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>73</v>
@@ -27064,18 +27083,18 @@
         <v>82</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="239" hidden="true">
+    <row r="239">
       <c r="A239" t="s" s="2">
         <v>682</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -27083,41 +27102,37 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G239" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I239" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J239" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N239" s="2"/>
       <c r="O239" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="P239" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q239" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="Q239" s="2"/>
       <c r="R239" t="s" s="2">
         <v>75</v>
       </c>
@@ -27137,13 +27152,13 @@
         <v>75</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y239" t="s" s="2">
-        <v>338</v>
+        <v>75</v>
       </c>
       <c r="Z239" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>75</v>
@@ -27161,7 +27176,7 @@
         <v>75</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>73</v>
@@ -27170,18 +27185,18 @@
         <v>82</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="240" hidden="true">
+    <row r="240">
       <c r="A240" t="s" s="2">
         <v>683</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -27195,7 +27210,7 @@
         <v>82</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>75</v>
@@ -27204,19 +27219,17 @@
         <v>83</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>75</v>
@@ -27265,7 +27278,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>73</v>
@@ -27274,18 +27287,18 @@
         <v>82</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>89</v>
+        <v>568</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="241" hidden="true">
+    <row r="241">
       <c r="A241" t="s" s="2">
         <v>684</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -27299,7 +27312,7 @@
         <v>82</v>
       </c>
       <c r="H241" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I241" t="s" s="2">
         <v>75</v>
@@ -27308,19 +27321,19 @@
         <v>83</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="P241" t="s" s="2">
         <v>75</v>
@@ -27330,7 +27343,7 @@
         <v>75</v>
       </c>
       <c r="S241" t="s" s="2">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>75</v>
@@ -27369,7 +27382,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>73</v>
@@ -27378,7 +27391,7 @@
         <v>82</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>355</v>
+        <v>75</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>90</v>
@@ -27389,15 +27402,17 @@
         <v>685</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C242" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="C242" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="D242" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G242" t="s" s="2">
         <v>82</v>
@@ -27412,19 +27427,19 @@
         <v>83</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>358</v>
+        <v>485</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>360</v>
+        <v>486</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>75</v>
@@ -27434,7 +27449,7 @@
         <v>75</v>
       </c>
       <c r="S242" t="s" s="2">
-        <v>75</v>
+        <v>571</v>
       </c>
       <c r="T242" t="s" s="2">
         <v>75</v>
@@ -27473,7 +27488,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>363</v>
+        <v>483</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>73</v>
@@ -27488,12 +27503,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
         <v>686</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -27507,7 +27522,7 @@
         <v>82</v>
       </c>
       <c r="H243" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I243" t="s" s="2">
         <v>75</v>
@@ -27516,20 +27531,16 @@
         <v>75</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>503</v>
+        <v>191</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O243" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N243" s="2"/>
+      <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>75</v>
       </c>
@@ -27553,13 +27564,13 @@
         <v>75</v>
       </c>
       <c r="X243" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>370</v>
+        <v>75</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>75</v>
@@ -27577,7 +27588,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>502</v>
+        <v>193</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>73</v>
@@ -27586,10 +27597,10 @@
         <v>82</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>372</v>
+        <v>75</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" hidden="true">
@@ -27597,11 +27608,11 @@
         <v>687</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
-        <v>374</v>
+        <v>126</v>
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
@@ -27620,20 +27631,18 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>376</v>
+        <v>195</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
         <v>75</v>
       </c>
@@ -27657,31 +27666,31 @@
         <v>75</v>
       </c>
       <c r="X244" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>379</v>
+        <v>75</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="AC244" t="s" s="2">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AD244" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>506</v>
+        <v>196</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>73</v>
@@ -27693,15 +27702,15 @@
         <v>89</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>90</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="245" hidden="true">
+    <row r="245">
       <c r="A245" t="s" s="2">
         <v>688</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27709,34 +27718,34 @@
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H245" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I245" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>76</v>
+        <v>326</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>508</v>
+        <v>327</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>509</v>
+        <v>328</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>414</v>
+        <v>329</v>
       </c>
       <c r="O245" t="s" s="2">
-        <v>415</v>
+        <v>330</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>75</v>
@@ -27785,23 +27794,753 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AG245" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH245" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI245" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ245" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="246" hidden="true">
+      <c r="A246" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C246" s="2"/>
+      <c r="D246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E246" s="2"/>
+      <c r="F246" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G246" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I246" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J246" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K246" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L246" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M246" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O246" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="P246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q246" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="R246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X246" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="Z246" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AA246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE246" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF246" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG246" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH246" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI246" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ246" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L247" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M247" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O247" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O248" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="P248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q248" s="2"/>
+      <c r="R248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S248" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G249" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H249" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J249" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K249" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L249" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M249" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N249" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q249" s="2"/>
+      <c r="R249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE249" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF249" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG249" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH249" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI249" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ249" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K250" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L250" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M250" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N250" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O250" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q250" s="2"/>
+      <c r="R250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="251" hidden="true">
+      <c r="A251" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="E251" s="2"/>
+      <c r="F251" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G251" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K251" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L251" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M251" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N251" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O251" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q251" s="2"/>
+      <c r="R251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X251" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z251" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG251" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH251" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI251" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AJ251" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="252" hidden="true">
+      <c r="A252" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AG245" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH245" t="s" s="2">
+      <c r="C252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E252" s="2"/>
+      <c r="F252" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G252" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AI245" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
+      <c r="H252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K252" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L252" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M252" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N252" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O252" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q252" s="2"/>
+      <c r="R252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG252" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH252" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI252" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ252" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ245">
+  <autoFilter ref="A1:AJ252">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27811,7 +28550,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI244">
+  <conditionalFormatting sqref="A2:AI251">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
